--- a/geezjobs_tracker.xlsx
+++ b/geezjobs_tracker.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V61"/>
+  <dimension ref="A1:V62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6767,6 +6767,73 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>operations-manager-geezjobs-recruitment-department-3</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>GEEZJOBS (RECRUITMENT DEPARTMENT)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ADDIS ABABA - ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>FULL-TIME</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>PERMANENT</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>7+ years</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Oct. 17, 2026 (15 days left)</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>https://geezjobs.com/job-detail/operations-manager-geezjobs-recruitment-department-3</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>GeezJobs</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1 hour ago</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:58:21 UTC</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>detail_page</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6778,7 +6845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6824,6 +6891,25 @@
         <v>60</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:58:24 UTC</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>61</v>
+      </c>
+      <c r="D3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/geezjobs_tracker.xlsx
+++ b/geezjobs_tracker.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V62"/>
+  <dimension ref="A1:V64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6834,6 +6834,393 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>health-manager-unicef</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Health Manager</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>UNICEF</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ADDIS ABABA - ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>FULL-TIME</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>PERMANENT</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Master or equivalent (Advanced University Degree) in public health, pediatric health, family health research, global/international health, health policy and/or management, vaccinology, environmental health sciences, biostatistics, socio-medical sciences, health education, epidemiology or another relevant field is required.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>8 Years</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Oct. 29, 2026 (26 days left)</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>https://geezjobs.com/job-detail/health-manager-unicef</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>GeezJobs</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>4 days ago</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:53:55 UTC</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>detail_page</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>UNICEF Ethiopia is seeking a highly qualified health professional to support the delivery of equitable and resilient health services for women and children. Operating within a decentralized and complex environment, the role will contribute to strengthening primary health care, immunization, health systems, and emergency preparedness and response, with a particular focus on reaching underserved, hard-to-reach, and crisis-affected populations across Ethiopia.
+Under the supervision of the Chief of Health, the Health Manager provides strategic leadership and technical oversight for the planning, implementation, monitoring, evaluation and reporting of UNICEF Ethiopia’s health programme, with a focus on immunization, primary health care, health systems strengthening, and health emergency preparedness and response. The position contributes to achieving equitable and sustainable health outcomes for women and children, particularly in underserved, fragile and emergency-affected settings.
+Key Functions and Accountabilities
+Programme development and planning.
+Programme management, monitoring and delivery of results.
+Advisory services and technical support.
+Advocacy, networking and partnership building.
+Innovation, knowledge management and capacity building.
+Minimum Requirements
+Education: Master or equivalent (Advanced University Degree) in public health, pediatric health, family health research, global/international health, health policy and/or management, vaccinology, environmental health sciences, biostatistics, socio-medical sciences, health education, epidemiology or another relevant field is required.
+Work Experience: At least 8 years of relevant work experience in public health programme planning and management is required, with demonstrated expertise in one or more of the following areas: health systems strengthening, immunization system support, primary health care, maternal and newborn health, health emergency and humanitarian preparedness and response, vaccine-preventable disease outbreak response, and public health emergencies.
+Skills: Strong expertise in primary health care (PHC), routine immunization, health system strengthening, disease outbreak response, health programme management, and the capacity to analyze surveillance and epidemiological data, immunization coverage trends and programme performance evidence.
+Language Requirements: Fluency in English is required.
+Desirable Qualifications and Experience
+Knowledge of another official UN language (Arabic, Chinese, French, Russian or Spanish) or a local language is an asset.
+Strong knowledge and direct experience of Ethiopia’s health system, including federal and regional structures, PHC service delivery, routine immunization, outbreak preparedness and response, humanitarian operating contexts and equity barriers, is highly desirable.
+Experience in Ethiopia or in a closely comparable large, decentralized, fragile and emergency-prone context will be considered a strong asset.
+Relevant experience in a UN system agency or international organization is considered an asset.
+Experience working with government counterparts, immunization and health emergency coordination platforms, donors and implementing partners is also desirable.
+Familiarity with global health initiatives and financing mechanisms, particularly Gavi, the Global Fund and other major bilateral and multilateral donors, as well as excellent skills in donor coordination, partnership management, resource mobilization, reporting and strategic communication, is highly desirable.
+Relevant experience at country level, particularly in development, fragile settings and humanitarian contexts.
+UNICEF Competencies Required
+Builds and maintains partnerships.
+Demonstrates self-awareness and ethical awareness.
+Drive to achieve results for impact.
+Innovates and embraces change.
+Manages ambiguity and complexity.
+Thinks and acts strategically.
+Works collaboratively with others.
+Nurtures, leads and manages people.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>veterinarian-elfora-agro-industries-plc</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Veterinarian</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ELFORA AGRO-INDUSTRIES PLC</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ADDIS ABABA - ETHIOPIA</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>FULL-TIME</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>PERMANENT</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>3/4 Years</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Oct. 7, 2026 (4 days left)</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>https://geezjobs.com/job-detail/veterinarian-elfora-agro-industries-plc</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>GeezJobs</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>4 days ago</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:53:55 UTC</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>detail_page</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>ELFORA Agro-Industries PLC is one of Ethiopia’s leading agro-processing companies, specializing in livestock production, meat processing, dairy farming, poultry production, and export of high-quality animal products. The company operates integrated farms, processing plants, and distribution systems across Ethiopia, supplying both local and international markets. ELFORA is committed to modern agricultural practices, quality, and safety standards.
+Education
+From recognized university/college second degree in Veterinary Medicine/Veterinary Microbiology or in other relevant field of study.
+From recognized university/college first degree in Veterinary Medicine/Veterinary Microbiology or in other relevant field of study.
+Experience
+1/2 years related work experience.
+3/4 years related work experience.
+HOW TO APPLY
+Interested applicant who meets the above requirements should submit their application with relevant documents and CV within 7 working days from the date of this vacancy announcement to ELFORA Main Office, Admin &amp; Human Resource Dep’t at 4th floor (You can apply at your current Operation).
+QUICK ACTIONS
+SAVE
+PRINT
+REPORT
+SHARE VACANCY
+Featured Jobs
+VIEW ALL
+FULL-TIME    |    PERMANENT
+@ MICRO PHARMA PLC
+የጥበቃ ሠራተኛ
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ KALWIN MULTISUPPLY PLC
+Front Desk Receptionist
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ GEEZJOBS (RECRUITMENT DEPARTMENT)
+Personal Driver (Female only)
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ RIVET PLC
+TECHNICAL COORDINATOR – ELEVATOR-LIFT
+Addis Ababa - ethiopia
+VIEW DETAILS
+PART-TIME    |    PERMANENT
+@ GEEZJOBS
+Trainer – Sales, Customer Service &amp; Basic IT Skills
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ ABBAHAWA TRADING PLC
+Senior Export Documentation Officer
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ TEMER PROPERTIES
+Project Health Safety And Environment Officer
+Addis Ababa - ethiopia
+VIEW DETAILS
+Y
+FULL-TIME    |    PERMANENT
+@ YSPANACEA TRADING
+Senior Accountant
+Addis Ababa, Kazanchis - ethiopia
+VIEW DETAILS
+A
+FULL-TIME    |    PERMANENT
+@ AGROCARE AGROCHEMICAL IMPORT
+Logistics Officer
+Addis Ababa - ethiopia
+VIEW DETAILS
+A
+FULL-TIME    |    CONTRACT
+@ AFRICAN MOSAIQUE
+Accountant &amp; Administration Officer
+Legetafo - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ MICRO PHARMA PLC
+የፅዳት ሠራተኛ / ክሊነር
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ HEILIG SCHOOL
+KG Division Main Teachers
+Addis Ababa - ethiopia
+VIEW DETAILS
+A
+FULL-TIME    |    PERMANENT
+@ ADIU COMMUNICATION SERVICE PLC
+Senior Sourcing And Transport Officer
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ ILLY
+Senior Accountant
+Addis Ababa - ethiopia
+VIEW DETAILS
+M
+FULL-TIME    |    PERMANENT
+@ MASSIDA SOLUTION PLC
+Logistics Business developer/Sales
+Addis Ababa, Ethiopia - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ SMILE SPECIALITY DENTAL CENTER
+People And Operations Manager
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ INFRA TECH SOFTWARE SERVICES
+IT Procurement And Tender Specialist
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ BETOPIA PROPERTIES MANAGEMENT PLC
+Architect
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ INTRACOM ICT SOLUTIONS
+Office Administrator
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ KALWIN MULTISUPPLY PLC
+Office Cleaner
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ INTERNATIONAL COMMUNITY SCHOOL OF ADDIS ABABA
+Maintenance Helper
+Addis Ababa - ethiopia
+VIEW DETAILS
+M
+FULL-TIME    |    PERMANENT
+@ MASSIDA SOLUTION PLC
+Client Account Manager &amp; Operations Coordinator
+Addis Ababa, Ethiopia - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ ENAT BANK
+Junior Customer Service Specialist
+Gelemso - ethiopia
+VIEW DETAILS
+Y
+FULL-TIME    |    PERMANENT
+@ YSPANACEA TRADING
+Senior International Tender &amp; Procurement Lead
+Addis Ababa, Kazanchis - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ EAST GATE GUEST HOUSE APARTMENT
+Receptionist
+Addis Ababa - ethiopia
+VIEW DETAILS
+A
+FULL-TIME    |    PERMANENT
+@ AGROCARE AGROCHEMICAL IMPORT
+Marketing And Sales And Promotion
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ GEEZJOBS (RECRUITMENT DEPARTMENT)
+Sales
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ GEEZJOBS (RECRUITMENT DEPARTMENT)
+Operations Manager
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ BETOPIA PROPERTIES MANAGEMENT PLC
+Construction Forman
+Addis Ababa - ethiopia
+VIEW DETAILS
+P
+FULL-TIME    |    PERMANENT
+@ PRINCESS TREATMENT
+Salon And Business Development Manager (Female only)
+Addis Ababa - ethiopia
+VIEW DETAILS
+S
+FULL-TIME    |    PERMANENT
+@ SUNNY REAL ESTATE
+Real Estate Sales Consultant
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ BETOPIA PROPERTIES MANAGEMENT PLC
+Site Engineer
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ HEILIG SCHOOL
+KG Division Child Care Aide
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ KALWIN MULTISUPPLY PLC
+Junior Accountant
+Addis Ababa - ethiopia
+VIEW DETAILS
+FULL-TIME    |    PERMANENT
+@ HEILIG SCHOOL
+KG Division Assistant Teacher
+Addis Ababa - ethiopia
+VIEW DETAILS
+M
+FULL-TIME    |    PERMANENT
+@ MACRO GENERAL CONTRACTOR
+Junior Project Accountant
+Addis Ababa - ethiopia
+VIEW DETAILS
+Install GeezJobs App
+Get faster access to jobs, instant alerts, and a better experience.
+Install</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6845,7 +7232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6910,6 +7297,25 @@
         <v>60</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:53:59 UTC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>63</v>
+      </c>
+      <c r="D4" t="n">
+        <v>59</v>
+      </c>
+      <c r="E4" t="n">
         <v>0</v>
       </c>
     </row>
